--- a/Output/Tables/Table_IQR_adjusted_malf.xlsx
+++ b/Output/Tables/Table_IQR_adjusted_malf.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/estela_blanco_uc_cl/Documents/Contaminación_Malformaciones Congénitas/LUR_DLNM/Output/Tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/estela_blanco_uc_cl/Documents/Contaminación_Malformaciones Congénitas/Pollution_Malformation_TEM/Output/Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_815F6508C45DFCA10236D0A04FF791F7B27DE505" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E6D8336-B947-6245-9D66-D36EE67DE222}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_815F6508C45DFCA10236D0A04FF791F7B27DE505" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{441713FD-DDF7-834B-89E3-46C37FE29AEB}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -795,6 +795,8 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
